--- a/documents/Uchebny_klass_OT_2027/02_Smeta_uchebny_klass_OT.xlsx
+++ b/documents/Uchebny_klass_OT_2027/02_Smeta_uchebny_klass_OT.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Эксплуатация" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Смета!$A$4:$I$67</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Смета!$A$4:$I$72</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="296">
   <si>
     <t xml:space="preserve">Свод бюджета: учебный класс по охране труда, новый корпус (2027)</t>
   </si>
@@ -93,10 +93,10 @@
     <t xml:space="preserve">Рекомендуемый вариант: Оптимальный.</t>
   </si>
   <si>
-    <t xml:space="preserve">Базовый: минимум для самостоятельного обучения по ПП 2464 (места обучения, практика ПП и СИЗ, СДО).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оптимальный: + специфика производства (макет ЧПУ, газоанализатор, СИЗОД для окрасочных камер), звук, видеофиксация.</t>
+    <t xml:space="preserve">Базовый: минимум для самостоятельного обучения по ПП 2464, включая работы на высоте и электробезопасность.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оптимальный: + макет ЧПУ, газоанализатор, СИЗОД для окрасочных камер, звук, видеофиксация.</t>
   </si>
   <si>
     <t xml:space="preserve">Расширенный: + VR-комплекс, интерактивная панель, лазерный тренажёр пожаротушения, сенсорный киоск.</t>
@@ -165,6 +165,18 @@
     <t xml:space="preserve">Допущение, перечень СИЗ, требующих практических навыков</t>
   </si>
   <si>
+    <t xml:space="preserve">Доля работников, выполняющих работы на высоте</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Допущение, уточнить по перечню работ на высоте</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Численность электротехнического персонала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Допущение, уточнить у главного энергетика</t>
+  </si>
+  <si>
     <t xml:space="preserve">Периодичность обучения</t>
   </si>
   <si>
@@ -213,6 +225,18 @@
     <t xml:space="preserve">Программа вводного инструктажа предприятия</t>
   </si>
   <si>
+    <t xml:space="preserve">Часы: работы на высоте (в классе)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теория и практика с СИЗ в классе (782н); практика на месте работ отдельно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Часы: электробезопасность (подготовка и проверка знаний)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежегодная проверка знаний электротехнического персонала</t>
+  </si>
+  <si>
     <t xml:space="preserve">Доля теории А/Б/В, проводимой очно в классе</t>
   </si>
   <si>
@@ -297,6 +321,12 @@
     <t xml:space="preserve">Вводный инструктаж (новые работники + подрядчики)</t>
   </si>
   <si>
+    <t xml:space="preserve">Безопасные методы работ на высоте</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Электробезопасность (ежегодно)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Итого чел.-часов в классе в год</t>
   </si>
   <si>
@@ -357,6 +387,18 @@
     <t xml:space="preserve">Витрины, манекены СИЗ, зеркало, макет (п. 39, 41 ПП 2464)</t>
   </si>
   <si>
+    <t xml:space="preserve">Практическая зона: работы на высоте</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стенд с анкерной линией, точка крепления 12 кН; потолок не ниже 3,5 м (782н)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Практическая зона: электробезопасность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стенд-макет, средства защиты в электроустановках</t>
+  </si>
+  <si>
     <t xml:space="preserve">Зона проверки знаний (АРМ)</t>
   </si>
   <si>
@@ -378,7 +420,7 @@
     <t xml:space="preserve">ИТОГО рекомендуемая площадь, м²</t>
   </si>
   <si>
-    <t xml:space="preserve">Вариант с объединением зоны проверки знаний с лекционной, м²</t>
+    <t xml:space="preserve">Минимально допустимо (зона проверки знаний совмещена с лекционной), м²</t>
   </si>
   <si>
     <t xml:space="preserve">Справочно: прежняя норма Минтруда (Пост. № 7 от 17.01.2001, утратило силу), м²</t>
@@ -720,13 +762,13 @@
     <t xml:space="preserve">СИЗОД с принудительной подачей воздуха (для окрасочных камер)</t>
   </si>
   <si>
-    <t xml:space="preserve">При наличии изоцианатных ЛКМ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Страховочная система (при наличии работ на высоте)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Только если есть работы на высоте</t>
+    <t xml:space="preserve">Нужен, если в паспортах безопасности ЛКМ есть изоцианаты (уточнить)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Комплект СИЗ от падения с высоты: удерживающая и страховочная системы, стропы с амортизатором, СЗС ползункового типа, анкерные ленты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Правила по ОТ при работе на высоте (Приказ Минтруда 782н); голосовое</t>
   </si>
   <si>
     <t xml:space="preserve">Комплект LOTO (станция, замки, блокираторы, бирки)</t>
@@ -762,13 +804,25 @@
     <t xml:space="preserve">Переносной 4-канальный газоанализатор (НКПР, O2, CO, H2S)</t>
   </si>
   <si>
-    <t xml:space="preserve">Голосовое; каналы уточнить под вещества окрасочных камер</t>
+    <t xml:space="preserve">Голосовое; каналы (в т.ч. ФИД для паров растворителей) уточнить по паспортам безопасности ЛКМ</t>
   </si>
   <si>
     <t xml:space="preserve">Стенд-макет по электробезопасности</t>
   </si>
   <si>
-    <t xml:space="preserve">При наличии электротехнического персонала</t>
+    <t xml:space="preserve">Электротехнический персонал (Правила по ОТ при эксплуатации электроустановок, Приказ Минтруда 903н)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Средства защиты в электроустановках до 1000 В (штанга изолирующая, переносное заземление, инструмент с изолирующими рукоятками) и плакаты по ЭБ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Практика применения средств защиты (Инструкция по применению СЗ в электроустановках, Приказ Минэнерго 1070)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Учебный стенд для работ на высоте (анкерная линия, точка крепления 12 кН, демонстрация фактора падения)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Практическая часть обучения безопасным методам работ на высоте (782н)</t>
   </si>
   <si>
     <t xml:space="preserve">Информационный сенсорный киоск у входа в корпус</t>
@@ -789,7 +843,25 @@
     <t xml:space="preserve">Обучение преподавателей и членов комиссии по программам А, Б, В</t>
   </si>
   <si>
-    <t xml:space="preserve">Комиссия по проверке знаний (ПП 2464)</t>
+    <t xml:space="preserve">Комиссия не менее 3 чел. + преподаватели (ПП 2464)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обучение преподавателей безопасным методам работ на высоте (3 группа, право проводить обучение)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Приказ Минтруда 782н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подготовка членов комиссии по электробезопасности (проверка знаний в Ростехнадзоре)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Приказ Минэнерго 796 (Правила работы с персоналом)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разработка учебных программ и материалов проверки знаний (А, Б, В, ПП, СИЗ, высота)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">П. 96 ПП 2464: программы утверждает работодатель</t>
   </si>
   <si>
     <t xml:space="preserve">ИТОГО по всем позициям</t>
@@ -1522,15 +1594,15 @@
         <v>6</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A5,Смета!$H$5:$H$67,"Б")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A5,Смета!$H$5:$H$72,"Б")</f>
         <v>1134000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A5,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A5,Смета!$H$5:$H$67,"О")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A5,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A5,Смета!$H$5:$H$72,"О")</f>
         <v>1169000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A5,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A5,Смета!$H$5:$H$67,"О")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A5,Смета!$H$5:$H$67,"Р")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A5,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A5,Смета!$H$5:$H$72,"О")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A5,Смета!$H$5:$H$72,"Р")</f>
         <v>1169000</v>
       </c>
     </row>
@@ -1539,15 +1611,15 @@
         <v>7</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A6,Смета!$H$5:$H$67,"Б")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A6,Смета!$H$5:$H$72,"Б")</f>
         <v>1105000</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A6,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A6,Смета!$H$5:$H$67,"О")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A6,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A6,Смета!$H$5:$H$72,"О")</f>
         <v>1470000</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A6,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A6,Смета!$H$5:$H$67,"О")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A6,Смета!$H$5:$H$67,"Р")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A6,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A6,Смета!$H$5:$H$72,"О")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A6,Смета!$H$5:$H$72,"Р")</f>
         <v>2470000</v>
       </c>
     </row>
@@ -1556,15 +1628,15 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A7,Смета!$H$5:$H$67,"Б")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A7,Смета!$H$5:$H$72,"Б")</f>
         <v>530000</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A7,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A7,Смета!$H$5:$H$67,"О")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A7,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A7,Смета!$H$5:$H$72,"О")</f>
         <v>530000</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A7,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A7,Смета!$H$5:$H$67,"О")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A7,Смета!$H$5:$H$67,"Р")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A7,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A7,Смета!$H$5:$H$72,"О")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A7,Смета!$H$5:$H$72,"Р")</f>
         <v>3080000</v>
       </c>
     </row>
@@ -1573,15 +1645,15 @@
         <v>9</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A8,Смета!$H$5:$H$67,"Б")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A8,Смета!$H$5:$H$72,"Б")</f>
         <v>731500</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A8,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A8,Смета!$H$5:$H$67,"О")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A8,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A8,Смета!$H$5:$H$72,"О")</f>
         <v>831500</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A8,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A8,Смета!$H$5:$H$67,"О")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A8,Смета!$H$5:$H$67,"Р")</f>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A8,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A8,Смета!$H$5:$H$72,"О")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A8,Смета!$H$5:$H$72,"Р")</f>
         <v>831500</v>
       </c>
     </row>
@@ -1590,16 +1662,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A9,Смета!$H$5:$H$67,"Б")</f>
-        <v>300000</v>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A9,Смета!$H$5:$H$72,"Б")</f>
+        <v>420000</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A9,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A9,Смета!$H$5:$H$67,"О")</f>
-        <v>475000</v>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A9,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A9,Смета!$H$5:$H$72,"О")</f>
+        <v>540000</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A9,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A9,Смета!$H$5:$H$67,"О")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A9,Смета!$H$5:$H$67,"Р")</f>
-        <v>475000</v>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A9,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A9,Смета!$H$5:$H$72,"О")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A9,Смета!$H$5:$H$72,"Р")</f>
+        <v>540000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,16 +1679,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A10,Смета!$H$5:$H$67,"Б")</f>
-        <v>328000</v>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A10,Смета!$H$5:$H$72,"Б")</f>
+        <v>673000</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A10,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A10,Смета!$H$5:$H$67,"О")</f>
-        <v>658000</v>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A10,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A10,Смета!$H$5:$H$72,"О")</f>
+        <v>938000</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A10,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A10,Смета!$H$5:$H$67,"О")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A10,Смета!$H$5:$H$67,"Р")</f>
-        <v>908000</v>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A10,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A10,Смета!$H$5:$H$72,"О")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A10,Смета!$H$5:$H$72,"Р")</f>
+        <v>1188000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1624,16 +1696,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A11,Смета!$H$5:$H$67,"Б")</f>
-        <v>81000</v>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A11,Смета!$H$5:$H$72,"Б")</f>
+        <v>335000</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A11,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A11,Смета!$H$5:$H$67,"О")</f>
-        <v>81000</v>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A11,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A11,Смета!$H$5:$H$72,"О")</f>
+        <v>335000</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A11,Смета!$H$5:$H$67,"Б")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A11,Смета!$H$5:$H$67,"О")+SUMIFS(Смета!$G$5:$G$67,Смета!$B$5:$B$67,$A11,Смета!$H$5:$H$67,"Р")</f>
-        <v>81000</v>
+        <f aca="false">SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A11,Смета!$H$5:$H$72,"Б")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A11,Смета!$H$5:$H$72,"О")+SUMIFS(Смета!$G$5:$G$72,Смета!$B$5:$B$72,$A11,Смета!$H$5:$H$72,"Р")</f>
+        <v>335000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1642,15 +1714,15 @@
       </c>
       <c r="B12" s="8" t="n">
         <f aca="false">SUM(B5:B11)</f>
-        <v>4209500</v>
+        <v>4928500</v>
       </c>
       <c r="C12" s="8" t="n">
         <f aca="false">SUM(C5:C11)</f>
-        <v>5214500</v>
+        <v>5813500</v>
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">SUM(D5:D11)</f>
-        <v>9014500</v>
+        <v>9613500</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1658,16 +1730,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="8" t="n">
-        <f aca="false">B12*'Исходные данные'!$B$24</f>
-        <v>336760</v>
+        <f aca="false">B12*'Исходные данные'!$B$28</f>
+        <v>394280</v>
       </c>
       <c r="C13" s="8" t="n">
-        <f aca="false">C12*'Исходные данные'!$B$24</f>
-        <v>417160</v>
+        <f aca="false">C12*'Исходные данные'!$B$28</f>
+        <v>465080</v>
       </c>
       <c r="D13" s="8" t="n">
-        <f aca="false">D12*'Исходные данные'!$B$24</f>
-        <v>721160</v>
+        <f aca="false">D12*'Исходные данные'!$B$28</f>
+        <v>769080</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1676,15 +1748,15 @@
       </c>
       <c r="B14" s="8" t="n">
         <f aca="false">B12+B13</f>
-        <v>4546260</v>
+        <v>5322780</v>
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">C12+C13</f>
-        <v>5631660</v>
+        <v>6278580</v>
       </c>
       <c r="D14" s="8" t="n">
         <f aca="false">D12+D13</f>
-        <v>9735660</v>
+        <v>10382580</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1692,16 +1764,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="8" t="n">
-        <f aca="false">B14*'Исходные данные'!$B$25</f>
-        <v>454626</v>
+        <f aca="false">B14*'Исходные данные'!$B$29</f>
+        <v>532278</v>
       </c>
       <c r="C15" s="8" t="n">
-        <f aca="false">C14*'Исходные данные'!$B$25</f>
-        <v>563166</v>
+        <f aca="false">C14*'Исходные данные'!$B$29</f>
+        <v>627858</v>
       </c>
       <c r="D15" s="8" t="n">
-        <f aca="false">D14*'Исходные данные'!$B$25</f>
-        <v>973566</v>
+        <f aca="false">D14*'Исходные данные'!$B$29</f>
+        <v>1038258</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1710,15 +1782,15 @@
       </c>
       <c r="B16" s="10" t="n">
         <f aca="false">B14+B15</f>
-        <v>5000886</v>
+        <v>5855058</v>
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">C14+C15</f>
-        <v>6194826</v>
+        <v>6906438</v>
       </c>
       <c r="D16" s="10" t="n">
         <f aca="false">D14+D15</f>
-        <v>10709226</v>
+        <v>11420838</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1732,8 +1804,8 @@
         <v>18</v>
       </c>
       <c r="B18" s="12" t="n">
-        <f aca="false">Площадь!E11</f>
-        <v>156</v>
+        <f aca="false">Площадь!E13</f>
+        <v>174</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1811,7 +1883,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
@@ -1944,56 +2016,56 @@
       <c r="A11" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="17" t="n">
-        <v>3</v>
+      <c r="B11" s="18" t="n">
+        <v>0.1</v>
       </c>
       <c r="C11" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>46</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" s="17" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="B14" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2004,21 +2076,21 @@
         <v>16</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>55</v>
-      </c>
-      <c r="B16" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>51</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>56</v>
@@ -2026,16 +2098,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" s="17" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2043,10 +2115,10 @@
         <v>59</v>
       </c>
       <c r="B18" s="17" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>60</v>
@@ -2056,11 +2128,11 @@
       <c r="A19" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="18" t="n">
-        <v>0.5</v>
+      <c r="B19" s="17" t="n">
+        <v>4</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>62</v>
@@ -2071,83 +2143,139 @@
         <v>63</v>
       </c>
       <c r="B20" s="17" t="n">
-        <v>247</v>
+        <v>1.5</v>
       </c>
       <c r="C20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>64</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="B21" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="16" t="s">
         <v>68</v>
-      </c>
-      <c r="B22" s="18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="16" t="s">
         <v>70</v>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>247</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>73</v>
-      </c>
-      <c r="B24" s="18" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="18" t="n">
-        <v>0.1</v>
+        <v>74</v>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>7</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D25" s="16" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2166,7 +2294,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -2176,7 +2304,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2185,7 +2313,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2201,35 +2329,35 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B5" s="20" t="n">
-        <f aca="false">ROUND('Исходные данные'!$B$5/'Исходные данные'!$B$11+'Исходные данные'!$B$5*'Исходные данные'!$B$6,0)</f>
+        <f aca="false">ROUND('Исходные данные'!$B$5/'Исходные данные'!$B$13+'Исходные данные'!$B$5*'Исходные данные'!$B$6,0)</f>
         <v>242</v>
       </c>
       <c r="C5" s="20" t="n">
-        <f aca="false">'Исходные данные'!$B$13</f>
+        <f aca="false">'Исходные данные'!$B$15</f>
         <v>16</v>
       </c>
       <c r="D5" s="21" t="n">
-        <f aca="false">'Исходные данные'!$B$19</f>
+        <f aca="false">'Исходные данные'!$B$23</f>
         <v>0.5</v>
       </c>
       <c r="E5" s="22" t="n">
@@ -2239,18 +2367,18 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B6" s="20" t="n">
-        <f aca="false">ROUND(('Исходные данные'!$B$5/'Исходные данные'!$B$11+'Исходные данные'!$B$5*'Исходные данные'!$B$6)*'Исходные данные'!$B$7,0)</f>
+        <f aca="false">ROUND(('Исходные данные'!$B$5/'Исходные данные'!$B$13+'Исходные данные'!$B$5*'Исходные данные'!$B$6)*'Исходные данные'!$B$7,0)</f>
         <v>169</v>
       </c>
       <c r="C6" s="20" t="n">
-        <f aca="false">'Исходные данные'!$B$14</f>
+        <f aca="false">'Исходные данные'!$B$16</f>
         <v>16</v>
       </c>
       <c r="D6" s="21" t="n">
-        <f aca="false">'Исходные данные'!$B$19</f>
+        <f aca="false">'Исходные данные'!$B$23</f>
         <v>0.5</v>
       </c>
       <c r="E6" s="22" t="n">
@@ -2260,18 +2388,18 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B7" s="20" t="n">
-        <f aca="false">ROUND(('Исходные данные'!$B$5/'Исходные данные'!$B$11+'Исходные данные'!$B$5*'Исходные данные'!$B$6)*'Исходные данные'!$B$8,0)</f>
+        <f aca="false">ROUND(('Исходные данные'!$B$5/'Исходные данные'!$B$13+'Исходные данные'!$B$5*'Исходные данные'!$B$6)*'Исходные данные'!$B$8,0)</f>
         <v>73</v>
       </c>
       <c r="C7" s="20" t="n">
-        <f aca="false">'Исходные данные'!$B$15</f>
+        <f aca="false">'Исходные данные'!$B$17</f>
         <v>16</v>
       </c>
       <c r="D7" s="21" t="n">
-        <f aca="false">'Исходные данные'!$B$19</f>
+        <f aca="false">'Исходные данные'!$B$23</f>
         <v>0.5</v>
       </c>
       <c r="E7" s="22" t="n">
@@ -2281,14 +2409,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B8" s="20" t="n">
-        <f aca="false">ROUND(('Исходные данные'!$B$5/'Исходные данные'!$B$11+'Исходные данные'!$B$5*'Исходные данные'!$B$6)*'Исходные данные'!$B$9,0)</f>
+        <f aca="false">ROUND(('Исходные данные'!$B$5/'Исходные данные'!$B$13+'Исходные данные'!$B$5*'Исходные данные'!$B$6)*'Исходные данные'!$B$9,0)</f>
         <v>193</v>
       </c>
       <c r="C8" s="20" t="n">
-        <f aca="false">'Исходные данные'!$B$16</f>
+        <f aca="false">'Исходные данные'!$B$18</f>
         <v>8</v>
       </c>
       <c r="D8" s="23" t="n">
@@ -2301,14 +2429,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B9" s="20" t="n">
-        <f aca="false">ROUND(('Исходные данные'!$B$5/'Исходные данные'!$B$11+'Исходные данные'!$B$5*'Исходные данные'!$B$6)*'Исходные данные'!$B$10,0)</f>
+        <f aca="false">ROUND(('Исходные данные'!$B$5/'Исходные данные'!$B$13+'Исходные данные'!$B$5*'Исходные данные'!$B$6)*'Исходные данные'!$B$10,0)</f>
         <v>169</v>
       </c>
       <c r="C9" s="20" t="n">
-        <f aca="false">'Исходные данные'!$B$17</f>
+        <f aca="false">'Исходные данные'!$B$19</f>
         <v>4</v>
       </c>
       <c r="D9" s="23" t="n">
@@ -2321,14 +2449,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B10" s="20" t="n">
-        <f aca="false">ROUND('Исходные данные'!$B$5*'Исходные данные'!$B$6+'Исходные данные'!$B$12,0)</f>
+        <f aca="false">ROUND('Исходные данные'!$B$5*'Исходные данные'!$B$6+'Исходные данные'!$B$14,0)</f>
         <v>175</v>
       </c>
       <c r="C10" s="20" t="n">
-        <f aca="false">'Исходные данные'!$B$18</f>
+        <f aca="false">'Исходные данные'!$B$20</f>
         <v>1.5</v>
       </c>
       <c r="D10" s="23" t="n">
@@ -2340,84 +2468,124 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="24" t="n">
-        <f aca="false">SUM(E5:E10)</f>
-        <v>6354.5</v>
+      <c r="A11" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="20" t="n">
+        <f aca="false">ROUND(('Исходные данные'!$B$5/'Исходные данные'!$B$13+'Исходные данные'!$B$5*'Исходные данные'!$B$6)*'Исходные данные'!$B$11,0)</f>
+        <v>24</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <f aca="false">'Исходные данные'!$B$21</f>
+        <v>16</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <f aca="false">B11*C11*D11</f>
+        <v>384</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="24" t="n">
-        <f aca="false">'Исходные данные'!$B$20*'Исходные данные'!$B$21*'Исходные данные'!$B$22</f>
-        <v>1296.75</v>
+      <c r="A12" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="20" t="n">
+        <f aca="false">'Исходные данные'!$B$12</f>
+        <v>25</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <f aca="false">'Исходные данные'!$B$22</f>
+        <v>8</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <f aca="false">B12*C12*D12</f>
+        <v>200</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="25" t="n">
-        <f aca="false">E11/E12</f>
-        <v>4.90032774243301</v>
+      <c r="E13" s="24" t="n">
+        <f aca="false">SUM(E5:E12)</f>
+        <v>6938.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="25" t="n">
-        <f aca="false">E13*'Исходные данные'!$B$23</f>
-        <v>12.2508193560825</v>
+      <c r="E14" s="24" t="n">
+        <f aca="false">'Исходные данные'!$B$24*'Исходные данные'!$B$25*'Исходные данные'!$B$26</f>
+        <v>1296.75</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="26" t="n">
-        <f aca="false">ROUNDUP('Исходные данные'!$B$5/100,0)</f>
-        <v>5</v>
+      <c r="E15" s="25" t="n">
+        <f aca="false">E13/E14</f>
+        <v>5.35068440331598</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="25" t="n">
+        <f aca="false">E15*'Исходные данные'!$B$27</f>
+        <v>13.37671100829</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="26" t="n">
+        <f aca="false">ROUNDUP('Исходные данные'!$B$5/100,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="27" t="n">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2434,7 +2602,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
@@ -2447,7 +2615,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2457,7 +2625,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2475,30 +2643,30 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B5" s="28" t="n">
-        <f aca="false">'Потребность в обучении'!$E$16</f>
+        <f aca="false">'Потребность в обучении'!$E$18</f>
         <v>24</v>
       </c>
       <c r="C5" s="29" t="n">
@@ -2512,12 +2680,12 @@
         <v>70</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B6" s="29" t="n">
         <v>2</v>
@@ -2533,12 +2701,12 @@
         <v>18</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B7" s="29" t="n">
         <v>1</v>
@@ -2554,33 +2722,33 @@
         <v>22</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B8" s="29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C8" s="29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E8" s="30" t="n">
         <f aca="false">B8*C8+D8</f>
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B9" s="29" t="n">
         <v>1</v>
@@ -2589,93 +2757,135 @@
         <v>0</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E9" s="30" t="n">
         <f aca="false">B9*C9+D9</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B10" s="29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C10" s="29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" s="30" t="n">
         <f aca="false">B10*C10+D10</f>
+        <v>30</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <f aca="false">B11*C11+D11</f>
+        <v>10</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32" t="n">
-        <f aca="false">SUM(E5:E10)</f>
-        <v>156</v>
-      </c>
-      <c r="F11" s="31"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="33" t="n">
-        <f aca="false">E11-E8</f>
-        <v>126</v>
-      </c>
-      <c r="F12" s="31"/>
+      <c r="E12" s="30" t="n">
+        <f aca="false">B12*C12+D12</f>
+        <v>6</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>117</v>
+      <c r="A13" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="32" t="n">
+        <f aca="false">SUM(E5:E12)</f>
+        <v>174</v>
+      </c>
+      <c r="F13" s="31"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="33" t="n">
+        <f aca="false">E13-E10</f>
+        <v>144</v>
+      </c>
+      <c r="F14" s="31"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="33" t="n">
         <f aca="false">24+MAX(0,ROUNDUP(('Исходные данные'!$B$5-1000)/1000,0))*6</f>
         <v>24</v>
       </c>
-      <c r="F13" s="31"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="F15" s="31"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2693,7 +2903,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2709,7 +2919,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2722,7 +2932,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2746,31 +2956,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2781,10 +2991,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>24</v>
@@ -2797,10 +3007,10 @@
         <v>336000</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2811,10 +3021,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E6" s="29" t="n">
         <v>30</v>
@@ -2827,10 +3037,10 @@
         <v>165000</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2841,10 +3051,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>1</v>
@@ -2857,10 +3067,10 @@
         <v>45000</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2871,10 +3081,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E8" s="29" t="n">
         <v>1</v>
@@ -2887,10 +3097,10 @@
         <v>35000</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2901,10 +3111,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E9" s="29" t="n">
         <v>4</v>
@@ -2917,10 +3127,10 @@
         <v>112000</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2931,10 +3141,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E10" s="29" t="n">
         <v>3</v>
@@ -2947,10 +3157,10 @@
         <v>135000</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2961,10 +3171,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E11" s="29" t="n">
         <v>4</v>
@@ -2977,10 +3187,10 @@
         <v>48000</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2991,10 +3201,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E12" s="29" t="n">
         <v>2</v>
@@ -3007,10 +3217,10 @@
         <v>44000</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3021,10 +3231,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E13" s="29" t="n">
         <v>6</v>
@@ -3037,10 +3247,10 @@
         <v>150000</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3051,10 +3261,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E14" s="29" t="n">
         <v>1</v>
@@ -3067,10 +3277,10 @@
         <v>15000</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3081,10 +3291,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E15" s="29" t="n">
         <v>4</v>
@@ -3097,10 +3307,10 @@
         <v>14000</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3111,10 +3321,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E16" s="29" t="n">
         <v>1</v>
@@ -3127,10 +3337,10 @@
         <v>70000</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3141,10 +3351,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E17" s="29" t="n">
         <v>1</v>
@@ -3157,10 +3367,10 @@
         <v>220000</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3171,10 +3381,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E18" s="29" t="n">
         <v>1</v>
@@ -3187,10 +3397,10 @@
         <v>130000</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3201,10 +3411,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E19" s="29" t="n">
         <v>6</v>
@@ -3217,10 +3427,10 @@
         <v>570000</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3231,10 +3441,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E20" s="29" t="n">
         <v>1</v>
@@ -3247,10 +3457,10 @@
         <v>60000</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3261,10 +3471,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E21" s="29" t="n">
         <v>1</v>
@@ -3277,10 +3487,10 @@
         <v>30000</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3291,10 +3501,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E22" s="29" t="n">
         <v>1</v>
@@ -3307,10 +3517,10 @@
         <v>15000</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3321,10 +3531,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E23" s="29" t="n">
         <v>1</v>
@@ -3337,10 +3547,10 @@
         <v>80000</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3351,10 +3561,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E24" s="29" t="n">
         <v>1</v>
@@ -3367,10 +3577,10 @@
         <v>120000</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3381,10 +3591,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E25" s="29" t="n">
         <v>1</v>
@@ -3397,10 +3607,10 @@
         <v>110000</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3411,10 +3621,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E26" s="29" t="n">
         <v>1</v>
@@ -3427,10 +3637,10 @@
         <v>45000</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3441,10 +3651,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E27" s="29" t="n">
         <v>1</v>
@@ -3457,10 +3667,10 @@
         <v>90000</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3471,10 +3681,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E28" s="29" t="n">
         <v>1</v>
@@ -3487,10 +3697,10 @@
         <v>750000</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3501,10 +3711,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E29" s="29" t="n">
         <v>1</v>
@@ -3517,10 +3727,10 @@
         <v>250000</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3531,10 +3741,10 @@
         <v>8</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E30" s="29" t="n">
         <v>1</v>
@@ -3547,10 +3757,10 @@
         <v>180000</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3561,10 +3771,10 @@
         <v>8</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="E31" s="29" t="n">
         <v>1</v>
@@ -3577,10 +3787,10 @@
         <v>350000</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3591,10 +3801,10 @@
         <v>8</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E32" s="29" t="n">
         <v>1</v>
@@ -3607,10 +3817,10 @@
         <v>2200000</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3621,10 +3831,10 @@
         <v>8</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E33" s="29" t="n">
         <v>1</v>
@@ -3637,10 +3847,10 @@
         <v>350000</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3651,10 +3861,10 @@
         <v>9</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E34" s="29" t="n">
         <v>1</v>
@@ -3667,10 +3877,10 @@
         <v>320000</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3681,10 +3891,10 @@
         <v>9</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E35" s="29" t="n">
         <v>2</v>
@@ -3697,10 +3907,10 @@
         <v>150000</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3711,10 +3921,10 @@
         <v>9</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E36" s="29" t="n">
         <v>1</v>
@@ -3727,10 +3937,10 @@
         <v>60000</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3741,10 +3951,10 @@
         <v>9</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E37" s="29" t="n">
         <v>1</v>
@@ -3757,10 +3967,10 @@
         <v>45000</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3771,10 +3981,10 @@
         <v>9</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E38" s="29" t="n">
         <v>1</v>
@@ -3787,10 +3997,10 @@
         <v>35000</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3801,10 +4011,10 @@
         <v>9</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E39" s="29" t="n">
         <v>2</v>
@@ -3817,10 +4027,10 @@
         <v>16000</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3831,10 +4041,10 @@
         <v>9</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E40" s="29" t="n">
         <v>1</v>
@@ -3847,10 +4057,10 @@
         <v>35000</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3861,10 +4071,10 @@
         <v>9</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E41" s="29" t="n">
         <v>3</v>
@@ -3877,10 +4087,10 @@
         <v>10500</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3891,10 +4101,10 @@
         <v>9</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E42" s="29" t="n">
         <v>1</v>
@@ -3907,10 +4117,10 @@
         <v>60000</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3921,10 +4131,10 @@
         <v>9</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E43" s="29" t="n">
         <v>1</v>
@@ -3937,10 +4147,10 @@
         <v>65000</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3951,10 +4161,10 @@
         <v>9</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E44" s="29" t="n">
         <v>1</v>
@@ -3967,10 +4177,10 @@
         <v>35000</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I44" s="16" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3981,10 +4191,10 @@
         <v>10</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E45" s="29" t="n">
         <v>2</v>
@@ -3997,10 +4207,10 @@
         <v>60000</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I45" s="16" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4011,10 +4221,10 @@
         <v>10</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E46" s="29" t="n">
         <v>1</v>
@@ -4027,10 +4237,10 @@
         <v>70000</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I46" s="16" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4041,10 +4251,10 @@
         <v>10</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E47" s="29" t="n">
         <v>1</v>
@@ -4057,10 +4267,10 @@
         <v>15000</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I47" s="16" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4071,10 +4281,10 @@
         <v>10</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E48" s="29" t="n">
         <v>1</v>
@@ -4087,10 +4297,10 @@
         <v>60000</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I48" s="16" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4101,10 +4311,10 @@
         <v>10</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E49" s="29" t="n">
         <v>1</v>
@@ -4117,10 +4327,10 @@
         <v>15000</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I49" s="16" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4131,10 +4341,10 @@
         <v>10</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E50" s="29" t="n">
         <v>1</v>
@@ -4147,10 +4357,10 @@
         <v>10000</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I50" s="16" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4161,10 +4371,10 @@
         <v>10</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E51" s="29" t="n">
         <v>1</v>
@@ -4177,10 +4387,10 @@
         <v>20000</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I51" s="16" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4191,10 +4401,10 @@
         <v>10</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E52" s="29" t="n">
         <v>1</v>
@@ -4207,10 +4417,10 @@
         <v>10000</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I52" s="16" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4221,10 +4431,10 @@
         <v>10</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E53" s="29" t="n">
         <v>1</v>
@@ -4237,10 +4447,10 @@
         <v>25000</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I53" s="16" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4251,10 +4461,10 @@
         <v>10</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E54" s="29" t="n">
         <v>1</v>
@@ -4267,10 +4477,10 @@
         <v>15000</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I54" s="16" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4281,10 +4491,10 @@
         <v>10</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E55" s="29" t="n">
         <v>1</v>
@@ -4297,13 +4507,13 @@
         <v>120000</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I55" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="16" t="n">
         <v>52</v>
       </c>
@@ -4311,26 +4521,26 @@
         <v>10</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E56" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="35" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="G56" s="36" t="n">
         <f aca="false">E56*F56</f>
-        <v>55000</v>
+        <v>120000</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I56" s="16" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4341,10 +4551,10 @@
         <v>11</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E57" s="29" t="n">
         <v>1</v>
@@ -4357,10 +4567,10 @@
         <v>75000</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I57" s="16" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4371,10 +4581,10 @@
         <v>11</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E58" s="29" t="n">
         <v>2</v>
@@ -4387,10 +4597,10 @@
         <v>12000</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4401,10 +4611,10 @@
         <v>11</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E59" s="29" t="n">
         <v>1</v>
@@ -4417,10 +4627,10 @@
         <v>30000</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I59" s="16" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4431,10 +4641,10 @@
         <v>11</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E60" s="29" t="n">
         <v>8</v>
@@ -4447,10 +4657,10 @@
         <v>176000</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I60" s="16" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4461,10 +4671,10 @@
         <v>11</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E61" s="29" t="n">
         <v>1</v>
@@ -4477,10 +4687,10 @@
         <v>35000</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I61" s="16" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4491,10 +4701,10 @@
         <v>11</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E62" s="29" t="n">
         <v>1</v>
@@ -4507,10 +4717,10 @@
         <v>180000</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I62" s="16" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4521,10 +4731,10 @@
         <v>11</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E63" s="29" t="n">
         <v>1</v>
@@ -4537,10 +4747,10 @@
         <v>85000</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I63" s="16" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4551,10 +4761,10 @@
         <v>11</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E64" s="29" t="n">
         <v>1</v>
@@ -4567,13 +4777,13 @@
         <v>65000</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I64" s="16" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="16" t="n">
         <v>61</v>
       </c>
@@ -4581,106 +4791,256 @@
         <v>11</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="E65" s="29" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="35" t="n">
-        <v>250000</v>
+        <v>60000</v>
       </c>
       <c r="G65" s="36" t="n">
         <f aca="false">E65*F65</f>
-        <v>250000</v>
+        <v>60000</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="I65" s="16" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="16" t="n">
         <v>62</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>250</v>
+        <v>143</v>
       </c>
       <c r="E66" s="29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" s="35" t="n">
-        <v>15000</v>
+        <v>220000</v>
       </c>
       <c r="G66" s="36" t="n">
         <f aca="false">E66*F66</f>
-        <v>45000</v>
+        <v>220000</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I66" s="16" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="16" t="n">
         <v>63</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>250</v>
+        <v>143</v>
       </c>
       <c r="E67" s="29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F67" s="35" t="n">
-        <v>12000</v>
+        <v>250000</v>
       </c>
       <c r="G67" s="36" t="n">
         <f aca="false">E67*F67</f>
-        <v>36000</v>
+        <v>250000</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="I67" s="16" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="38" t="n">
-        <f aca="false">SUM(G5:G67)</f>
-        <v>9014500</v>
-      </c>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
+      <c r="A68" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="E68" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" s="35" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G68" s="36" t="n">
+        <f aca="false">E68*F68</f>
+        <v>45000</v>
+      </c>
+      <c r="H68" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="I68" s="16" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="E69" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" s="35" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G69" s="36" t="n">
+        <f aca="false">E69*F69</f>
+        <v>60000</v>
+      </c>
+      <c r="H69" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="I69" s="16" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="E70" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" s="35" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G70" s="36" t="n">
+        <f aca="false">E70*F70</f>
+        <v>50000</v>
+      </c>
+      <c r="H70" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="I70" s="16" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="E71" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" s="35" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G71" s="36" t="n">
+        <f aca="false">E71*F71</f>
+        <v>30000</v>
+      </c>
+      <c r="H71" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="I71" s="16" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E72" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="35" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G72" s="36" t="n">
+        <f aca="false">E72*F72</f>
+        <v>150000</v>
+      </c>
+      <c r="H72" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="38" t="n">
+        <f aca="false">SUM(G5:G72)</f>
+        <v>9613500</v>
+      </c>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I67"/>
+  <autoFilter ref="A4:I72"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4707,14 +5067,14 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4726,21 +5086,21 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="C5" s="35" t="n">
         <v>300000</v>
@@ -4748,10 +5108,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="C6" s="35" t="n">
         <v>60000</v>
@@ -4759,10 +5119,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="C7" s="35" t="n">
         <v>60000</v>
@@ -4770,10 +5130,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="C8" s="35" t="n">
         <v>40000</v>
@@ -4781,10 +5141,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="C9" s="35" t="n">
         <v>50000</v>
@@ -4792,10 +5152,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="C10" s="35" t="n">
         <v>30000</v>
@@ -4803,7 +5163,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="38" t="n">
